--- a/Excel/EquipSpeicalConfig.xlsx
+++ b/Excel/EquipSpeicalConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="67">
   <si>
     <t>#</t>
   </si>
@@ -204,6 +209,30 @@
   </si>
   <si>
     <t>50000,15,3,2</t>
+  </si>
+  <si>
+    <t>2,1002,22,2002,10002</t>
+  </si>
+  <si>
+    <t>26000,210,80,20,1</t>
+  </si>
+  <si>
+    <t>10000,50,16,4,1</t>
+  </si>
+  <si>
+    <t>3,1003,24,2003,10003</t>
+  </si>
+  <si>
+    <t>1,1001,27,2001,10001</t>
+  </si>
+  <si>
+    <t>520000,210,40,20,1</t>
+  </si>
+  <si>
+    <t>200000,50,8,4,1</t>
+  </si>
+  <si>
+    <t>1,1001,28,2001,10001</t>
   </si>
 </sst>
 </file>
@@ -1179,7 +1208,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFB19"/>
+  <dimension ref="A1:XFB24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1651,16 +1680,16 @@
         <v>10000</v>
       </c>
       <c r="V9" s="1">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="W9" s="1">
+        <v>16</v>
+      </c>
+      <c r="X9" s="1">
         <v>8</v>
       </c>
-      <c r="X9" s="1">
+      <c r="Y9" s="1">
         <v>4</v>
-      </c>
-      <c r="Y9" s="1">
-        <v>3</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:25 16375:16382">
@@ -1879,22 +1908,22 @@
       <c r="O14" s="1">
         <v>5014</v>
       </c>
-      <c r="T14" s="2">
-        <v>0</v>
-      </c>
-      <c r="U14" s="2">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2">
-        <v>0</v>
-      </c>
-      <c r="W14" s="2">
-        <v>0</v>
-      </c>
-      <c r="X14" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="2">
+      <c r="T14" s="1">
+        <v>2000</v>
+      </c>
+      <c r="U14" s="1">
+        <v>100</v>
+      </c>
+      <c r="V14" s="1">
+        <v>5</v>
+      </c>
+      <c r="W14" s="1">
+        <v>2</v>
+      </c>
+      <c r="X14" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="1">
         <v>0</v>
       </c>
       <c r="XEU14" s="1"/>
@@ -1921,27 +1950,27 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="T15" s="2">
-        <f t="shared" ref="T15:Y15" si="0">T14+T6*5+T7</f>
+        <f t="shared" ref="T15:T18" si="0">T14+T6*4+T7</f>
         <v>20000</v>
       </c>
       <c r="U15" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="U15:Y15" si="1">U14+U6*4+U7</f>
         <v>1000</v>
       </c>
       <c r="V15" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="W15" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="X15" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="Y15" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="XEU15" s="1"/>
@@ -1994,27 +2023,21 @@
         <v>5011</v>
       </c>
       <c r="T16" s="2">
-        <f t="shared" ref="T16:Y16" si="1">T15+T7*5+T8</f>
         <v>120000</v>
       </c>
       <c r="U16" s="2">
-        <f t="shared" si="1"/>
         <v>6000</v>
       </c>
       <c r="V16" s="2">
-        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="W16" s="2">
-        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="X16" s="2">
-        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="Y16" s="2">
-        <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
@@ -2059,28 +2082,28 @@
         <v>5012</v>
       </c>
       <c r="T17" s="2">
-        <f t="shared" ref="T17:Y17" si="2">T16+T8*5+T9</f>
-        <v>570000</v>
+        <f t="shared" si="0"/>
+        <v>520000</v>
       </c>
       <c r="U17" s="2">
-        <f t="shared" si="2"/>
-        <v>28500</v>
+        <f t="shared" ref="U17:Y17" si="2">U16+U8*4+U9</f>
+        <v>26000</v>
       </c>
       <c r="V17" s="2">
         <f t="shared" si="2"/>
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="W17" s="2">
         <f t="shared" si="2"/>
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="X17" s="2">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y17" s="2">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:25">
@@ -2162,6 +2185,170 @@
         <v>58</v>
       </c>
       <c r="O19" s="1">
+        <v>5014</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:25">
+      <c r="C21" s="1">
+        <v>13</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>101</v>
+      </c>
+      <c r="F21" s="1">
+        <v>40</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1001</v>
+      </c>
+      <c r="H21" s="1">
+        <v>4</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J21" s="5">
+        <v>15</v>
+      </c>
+      <c r="K21" s="5">
+        <v>19</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="O21" s="1">
+        <v>5011</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:25">
+      <c r="C22" s="1">
+        <v>14</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1">
+        <v>101</v>
+      </c>
+      <c r="F22" s="1">
+        <v>40</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1002</v>
+      </c>
+      <c r="H22" s="1">
+        <v>4</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J22" s="5">
+        <v>15</v>
+      </c>
+      <c r="K22" s="5">
+        <v>19</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="O22" s="1">
+        <v>5012</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:25">
+      <c r="C23" s="1">
+        <v>15</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3</v>
+      </c>
+      <c r="E23" s="1">
+        <v>101</v>
+      </c>
+      <c r="F23" s="1">
+        <v>40</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1003</v>
+      </c>
+      <c r="H23" s="1">
+        <v>4</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J23" s="5">
+        <v>15</v>
+      </c>
+      <c r="K23" s="5">
+        <v>19</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="O23" s="1">
+        <v>5013</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:25">
+      <c r="C24" s="1">
+        <v>16</v>
+      </c>
+      <c r="D24" s="1">
+        <v>4</v>
+      </c>
+      <c r="E24" s="1">
+        <v>101</v>
+      </c>
+      <c r="F24" s="1">
+        <v>40</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1004</v>
+      </c>
+      <c r="H24" s="1">
+        <v>4</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J24" s="5">
+        <v>15</v>
+      </c>
+      <c r="K24" s="5">
+        <v>19</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="O24" s="1">
         <v>5014</v>
       </c>
     </row>

--- a/Excel/EquipSpeicalConfig.xlsx
+++ b/Excel/EquipSpeicalConfig.xlsx
@@ -2205,7 +2205,7 @@
         <v>1001</v>
       </c>
       <c r="H21" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>25</v>
@@ -2246,7 +2246,7 @@
         <v>1002</v>
       </c>
       <c r="H22" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>30</v>
@@ -2287,7 +2287,7 @@
         <v>1003</v>
       </c>
       <c r="H23" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>34</v>
@@ -2328,7 +2328,7 @@
         <v>1004</v>
       </c>
       <c r="H24" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>40</v>

--- a/Excel/EquipSpeicalConfig.xlsx
+++ b/Excel/EquipSpeicalConfig.xlsx
@@ -2214,7 +2214,7 @@
         <v>15</v>
       </c>
       <c r="K21" s="5">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>59</v>
@@ -2255,7 +2255,7 @@
         <v>15</v>
       </c>
       <c r="K22" s="5">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>62</v>
@@ -2296,7 +2296,7 @@
         <v>15</v>
       </c>
       <c r="K23" s="5">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L23" s="7" t="s">
         <v>63</v>
@@ -2337,7 +2337,7 @@
         <v>15</v>
       </c>
       <c r="K24" s="5">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>66</v>
